--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-11_User_Access_Maintenance/04_BIBS_TestPlan_BRD-11_User_Access_Maintenance_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-11_User_Access_Maintenance/04_BIBS_TestPlan_BRD-11_User_Access_Maintenance_v2.0.xlsx
@@ -9485,7 +9485,7 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>A database update or delete of a log row is refused.</t>
+          <t>An attempt to change or delete a log entry outside the screens is refused.</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Reports and logs. The four access reports and the insert-only access-change log.</t>
+          <t>Reports and logs. The four access reports and the access-change log that no user can change.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -11147,12 +11147,12 @@
       <c r="K17" s="12" t="inlineStr">
         <is>
           <t>1. Enter the Windows ID of requestor and the test directory password.
-2. As the database administrator check the password column of requestor.</t>
+2. As the infrastructure administrator check the stored sign-in data of requestor.</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>The home page opens with the Requestor menu; no password is stored for requestor.</t>
+          <t>The home page opens with the Requestor menu; no password is kept for requestor.</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Token of an ended session</t>
+          <t>Action of an ended session</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>1. Keep the sign-in of requestor; log out; send a direct request with the old sign-in.</t>
+          <t>1. Keep the sign-in of requestor; log out; repeat an action of the old session outside the screens.</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>The password date of requestor is set 90 days back in the test database.
+          <t>The password date of requestor is set 90 days back in the test environment.
 Data: TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
@@ -12505,7 +12505,7 @@
       <c r="I35" s="12" t="inlineStr"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>The test lead sets the last sign-in of subject user a013000104 to 91 days ago (database console).
+          <t>The test lead sets the last sign-in of subject user a013000104 to 91 days ago (administration tools of the test environment).
 Data: TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
         </is>
       </c>
@@ -12872,7 +12872,7 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr"/>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I53" s="12" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr"/>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr"/>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I66" s="12" t="inlineStr"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I70" s="12" t="inlineStr"/>
@@ -15453,7 +15453,7 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr"/>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr"/>
@@ -18555,7 +18555,7 @@
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I115" s="12" t="inlineStr"/>
@@ -18628,7 +18628,7 @@
       </c>
       <c r="H116" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I116" s="12" t="inlineStr"/>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="H142" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I142" s="12" t="inlineStr"/>
@@ -22878,7 +22878,7 @@
       </c>
       <c r="E172" s="12" t="inlineStr">
         <is>
-          <t>Database update of a log row</t>
+          <t>Change of a log entry outside the screens</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
@@ -22893,7 +22893,7 @@
       </c>
       <c r="H172" s="12" t="inlineStr">
         <is>
-          <t>Database console of the test environment (database administrator)</t>
+          <t>Administration tools of the test environment (infrastructure administrator)</t>
         </is>
       </c>
       <c r="I172" s="12" t="inlineStr"/>
@@ -22904,12 +22904,12 @@
       </c>
       <c r="K172" s="12" t="inlineStr">
         <is>
-          <t>1. As the database administrator run an UPDATE and a DELETE on a row of the access-change log.</t>
+          <t>1. As the infrastructure administrator try to change and then to delete an entry of the access-change log directly.</t>
         </is>
       </c>
       <c r="L172" s="12" t="inlineStr">
         <is>
-          <t>The database refuses both.</t>
+          <t>Both attempts are refused and the entry is unchanged.</t>
         </is>
       </c>
       <c r="M172" s="12" t="inlineStr">
@@ -23188,7 +23188,7 @@
       <c r="I176" s="12" t="inlineStr"/>
       <c r="J176" s="12" t="inlineStr">
         <is>
-          <t>The test lead makes the job fail (for example by revoking its database grant on the test environment).
+          <t>The test lead makes the job fail (for example by withdrawing its access to the records it updates in the test environment).
 Data: TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Keep a structured, insert-only access-change log</t>
+          <t>Keep an access-change log that no user can change</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">

--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-11_User_Access_Maintenance/04_BIBS_TestPlan_BRD-11_User_Access_Maintenance_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-11_User_Access_Maintenance/04_BIBS_TestPlan_BRD-11_User_Access_Maintenance_v2.0.xlsx
@@ -5805,7 +5805,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>A deactivated user is refused with its own message and the attempt is not counted.</t>
+          <t>A deactivated user is refused with the same message as a wrong password and the attempt is not counted.</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -10466,8 +10466,8 @@
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>The account is locked; the fourth attempt is refused.
-Message "Account is locked. Contact your administrator.".</t>
+          <t>The account is locked; the fourth attempt, with the correct password, is refused with the same message as a wrong password; Users shows the account as locked to the System Administrator.
+Message "Invalid user name or password".</t>
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr">
@@ -10543,8 +10543,8 @@
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>Both attempts are refused with the deactivated message; the failed-attempt count stays 0 and the account is not locked.
-Message "Your account is deactivated. Contact your administrator.".</t>
+          <t>Both attempts are refused with the same message as a wrong password; the failed-attempt count stays 0 and the account is not locked.
+Message "Invalid user name or password".</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
@@ -23895,7 +23895,7 @@
       <c r="L185" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-UA-07 New Request and Edit Request (user requests) of the FRS.
-Fields in this order: 1 Request Type (Drop-down, mandatory Y); 2 User Type (Drop-down, mandatory Y); 3 Effective Date (Date, mandatory N); 4 User ID (Text (new user); Drop-down (existing user), mandatory Y); 5 Full Name (Text, mandatory Cond.: enrolment); 6 E-mail (E-mail, mandatory N); 7 Windows ID (Text, mandatory N); 8 Home Branch (Drop-down, mandatory N); 9 Business Unit Group (Drop-down, mandatory N); 10 User Level (Drop-down, mandatory N); 11 Authorisation Limit (PHP) (Amount, mandatory N); 12 Group profile check boxes (Check boxes, mandatory Cond.: enrolment (at least one)); 13 Reason (Drop-down, mandatory N); 14 Also unlock the account (Check box, mandatory N); 15 Approver (Drop-down, mandatory Y); 16 Remarks (Justification) (Text area, mandatory Y); 17 Correction Remarks (Text area, mandatory Cond.: resubmission).
+Fields in this order: 1 Request Type (Drop-down, mandatory Y); 2 User Type (Drop-down, mandatory Y); 3 Effective Date (Date, mandatory N); 4 User ID (Text (new user); Drop-down (existing user), mandatory Y); 5 Full Name (Text, mandatory Cond.: enrolment); 6 E-mail (E-mail, mandatory N); 7 Windows ID (Text, mandatory N); 8 Home Branch (Drop-down, mandatory N); 9 Business Unit Group (Drop-down, mandatory N); 10 User Level (Drop-down, mandatory N); 11 Authorisation Limit (PHP) (Amount, mandatory N); 12 Search group profiles (Text, mandatory N); 13 Group profile check boxes (Check boxes, mandatory Cond.: enrolment (at least one)); 14 Reason (Drop-down, mandatory N); 15 Also unlock the account (Check box, mandatory N); 16 Approver (Drop-down, mandatory Y); 17 Remarks (Justification) (Text area, mandatory Y); 18 Correction Remarks (Text area, mandatory Cond.: resubmission).
 Actions: Cancel; Save Draft; Submit; Resubmit.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -23974,7 +23974,7 @@
       <c r="L186" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-UA-08 Access Request record of the FRS.
-Fields in this order: 1 Title (Text, mandatory -); 2 Request (Reference chip, mandatory -); 3 Status and risk flags (Pill and tags, mandatory -); 4 Requested (Text, mandatory -); 5 Approver (Text, mandatory -); 6 Effective (Date, mandatory -); 7 Decision (Text, mandatory -); 8 Attribute / Current / Requested (Table, mandatory -); 9 Remarks / Effective date / Reason / Members / Could not be applied (Text, mandatory -); 10 Order / Approver / Decision / Remarks / Decided (Table, mandatory -); 11 Date / Action / Status / By / Remarks (Table, mandatory -); 12 Comment / Remarks / Reason (Text area, mandatory Cond.: Return, Reject, Cancel).
+Fields in this order: 1 Title (Text, mandatory -); 2 Request (Reference chip, mandatory -); 3 Status and risk flags (Pill and tags, mandatory -); 4 Requested By (Text, mandatory -); 5 Requested On (Date and time, mandatory -); 6 Approver (Text, mandatory -); 7 Effective (Date, mandatory -); 8 Decision (Text, mandatory -); 9 Attribute / Current / Requested (Table, mandatory -); 10 Group Profile / Change (Table, mandatory -); 11 Remarks / Effective date / Reason / Members / Could not be applied (Text, mandatory -); 12 Order / Approver / Decision / Remarks / Decided (Table, mandatory -); 13 Date / Action / Status / By / Remarks (Table, mandatory -); 14 Comment / Remarks / Reason (Text area, mandatory Cond.: Return, Reject, Cancel).
 Actions: Edit Request; Cancel Request; Approve and Apply; Second Approval; Return; Reject; Implement Request.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -24130,7 +24130,7 @@
       <c r="L188" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-UA-10 Bulk Request Batch of the FRS.
-Fields in this order: 1 Batch (Reference chip, mandatory -); 2 Requested (Text, mandatory -); 3 Request / Type / User / Change / Status / Error (Table, mandatory -); 4 Approver (Drop-down, mandatory Y); 5 Remarks (Text area, mandatory Y).
+Fields in this order: 1 Batch (Reference chip, mandatory -); 2 Requested By (Text, mandatory -); 3 Requested On (Date and time, mandatory -); 4 Request / Type / User / Change / Status / Error (Table, mandatory -); 5 Approver (Drop-down, mandatory Y); 6 Remarks (Text area, mandatory Y).
 Actions: Submit Batch; Approve Batch; Return Batch; Reject Batch; Cancel Batch; Open a line.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -24908,11 +24908,9 @@
       <c r="L198" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-001: "Account is locked. Contact your administrator." (AUTHENTICATION_FAILED)
-MSG-UA-002: "Invalid token" (AUTHENTICATION_FAILED)
-MSG-UA-003: "Invalid user name or password" (AUTHENTICATION_FAILED)
-MSG-UA-004: "Your account is deactivated. Contact your administrator." (AUTHENTICATION_FAILED)
-MSG-UA-005: "Too many sign-in attempts. Wait a minute and try again." (LOGIN_RATE_LIMITED)</t>
+MSG-UA-001: "Invalid token" (AUTHENTICATION_FAILED)
+MSG-UA-002: "Too many sign-in attempts. Wait a minute and try again." (LOGIN_RATE_LIMITED)
+MSG-UA-003: "Too many password reset requests. Wait a few minutes and try again." (RESET_RATE_LIMITED)</t>
         </is>
       </c>
       <c r="M198" s="12" t="inlineStr">
@@ -24987,10 +24985,10 @@
       <c r="L199" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-006: "Current password is incorrect" (INVALID_PASSWORD)
-MSG-UA-007: "This password reset link has expired. Request a new one" (RESET_LINK_EXPIRED)
-MSG-UA-008: "This password reset link is not valid or was already used" (RESET_LINK_INVALID)
-MSG-UA-009: "Unknown user" (UNKNOWN_USER)</t>
+MSG-UA-004: "Current password is incorrect" (INVALID_PASSWORD)
+MSG-UA-005: "This password reset link has expired. Request a new one" (RESET_LINK_EXPIRED)
+MSG-UA-006: "This password reset link is not valid or was already used" (RESET_LINK_INVALID)
+MSG-UA-007: "Unknown user" (UNKNOWN_USER)</t>
         </is>
       </c>
       <c r="M199" s="12" t="inlineStr">
@@ -25065,17 +25063,17 @@
       <c r="L200" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-010: "A digit"
-MSG-UA-011: "A lower-case letter"
-MSG-UA-012: "A symbol"
-MSG-UA-013: "An upper-case letter"
-MSG-UA-014: "At least 10 characters"
-MSG-UA-015: "Both new passwords must match"
-MSG-UA-017: "Your password is older&lt;age&gt; and has expired. Choose a new password to continue."
-MSG-UA-018: "Your password was set by an administrator. Choose your own password to continue."
-MSG-UA-019: "You changed your password less than a day / &lt;min age&gt; days ago" (PASSWORD_CHANGED_TOO_SOON)
-MSG-UA-020: "Your password is managed by the BDO directory; change it there" (PASSWORD_MANAGED_BY_DIRECTORY)
-MSG-UA-021: "You used this password recently. Choose another one" (PASSWORD_REUSED)</t>
+MSG-UA-008: "A digit"
+MSG-UA-009: "A lower-case letter"
+MSG-UA-010: "A symbol"
+MSG-UA-011: "An upper-case letter"
+MSG-UA-012: "At least 10 characters"
+MSG-UA-013: "Both new passwords must match"
+MSG-UA-015: "Your password is older&lt;age&gt; and has expired. Choose a new password to continue."
+MSG-UA-016: "Your password was set by an administrator. Choose your own password to continue."
+MSG-UA-017: "You changed your password less than a day / &lt;min age&gt; days ago" (PASSWORD_CHANGED_TOO_SOON)
+MSG-UA-018: "Your password is managed by the corporate directory; change it there" (PASSWORD_MANAGED_BY_DIRECTORY)
+MSG-UA-019: "You used this password recently. Choose another one" (PASSWORD_REUSED)</t>
         </is>
       </c>
       <c r="M200" s="12" t="inlineStr">
@@ -25150,10 +25148,10 @@
       <c r="L201" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-022: "You were signed out after &lt;timeout minutes&gt; minutes of inactivity."
-MSG-UA-023: "Your session has ended. Please sign in again."
-MSG-UA-024: "Session not found: &lt;session id&gt;" (NOT_FOUND)
-MSG-UA-025: "The session has already ended" (SESSION_ALREADY_ENDED)</t>
+MSG-UA-020: "You were signed out after &lt;timeout minutes&gt; minutes of inactivity."
+MSG-UA-021: "Your session has ended. Please sign in again."
+MSG-UA-022: "Session not found: &lt;session id&gt;" (NOT_FOUND)
+MSG-UA-023: "The session has already ended" (SESSION_ALREADY_ENDED)</t>
         </is>
       </c>
       <c r="M201" s="12" t="inlineStr">
@@ -25228,11 +25226,11 @@
       <c r="L202" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-026: "&lt;email&gt; is not a valid e-mail address"
-MSG-UA-028: "Enter the mobile number with digits only, for example +63 917 123 4567"
-MSG-UA-029: "Enter your e-mail address"
-MSG-UA-032: "Check the highlighted fields" (PROFILE_INVALID)
-MSG-UA-033: "Unknown user" (UNKNOWN_USER)</t>
+MSG-UA-024: "&lt;email&gt; is not a valid e-mail address"
+MSG-UA-026: "Enter the mobile number with digits only, for example +63 917 123 4567"
+MSG-UA-027: "Enter your e-mail address"
+MSG-UA-030: "Check the highlighted fields" (PROFILE_INVALID)
+MSG-UA-031: "Unknown user" (UNKNOWN_USER)</t>
         </is>
       </c>
       <c r="M202" s="12" t="inlineStr">
@@ -25295,7 +25293,7 @@
       <c r="L203" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-034: "Approve &lt;reference&gt; on its own: the new user's temporary password is shown once" (ACCESS_APPROVE_INDIVIDUALLY)</t>
+MSG-UA-032: "Approve &lt;reference&gt; on its own: the new user's temporary password is shown once" (ACCESS_APPROVE_INDIVIDUALLY)</t>
         </is>
       </c>
       <c r="M203" s="12" t="inlineStr">
@@ -25370,59 +25368,59 @@
       <c r="L204" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-038: "Add at least one approver"
-MSG-UA-039: "Enter an amount of zero or more, with up to 2 decimals"
-MSG-UA-040: "Enter the full name of the new user"
-MSG-UA-041: "Enter the justification"
-MSG-UA-042: "Enter the name of the group profile"
-MSG-UA-043: "Enter the party code"
-MSG-UA-044: "Enter the profile code"
-MSG-UA-045: "Grant or withdraw at least one permission"
-MSG-UA-046: "Select an existing user"
-MSG-UA-047: "Select at least one permission"
-MSG-UA-048: "Select at least one role"
-MSG-UA-049: "Select the approver"
-MSG-UA-050: "Select the insurer or client"
-MSG-UA-051: "Select the role to change"
-MSG-UA-052: "The effective date cannot be before today"
-MSG-UA-053: "The user ID does not have the BDOI format"
-MSG-UA-054: "The user ID must be &lt;user id format text&gt;"
-MSG-UA-055: "This user already exists"
-MSG-UA-056: "This user is already active"
-MSG-UA-057: "This user is already deactivated"
-MSG-UA-058: "Use 3 to 50 letters, digits, dots, dashes or underscores"
-MSG-UA-059: "Use up to 40 capital letters, digits or underscores"
-MSG-UA-060: "&lt;name&gt; cannot approve this request" (ACCESS_APPROVER_NOT_ELIGIBLE)
-MSG-UA-061: "Add at least one approver" (ACCESS_APPROVER_REQUIRED)
-MSG-UA-062: "Select the approver" (ACCESS_APPROVER_REQUIRED)
-MSG-UA-063: "&lt;name&gt; is already an approver of this request" (ACCESS_APPROVER_TWICE)
-MSG-UA-064: "Enter the correction remarks" (ACCESS_CORRECTION_REMARKS)
-MSG-UA-065: "The effective date cannot be before today" (ACCESS_EFFECTIVE_DATE)
-MSG-UA-066: "An effective date applies to user requests; group profiles are implemented" (ACCESS_EFFECTIVE_DATE_USER_ONLY)
-MSG-UA-067: "Select the insurer or client of the external user" (ACCESS_EXTERNAL_PARTY)
-MSG-UA-068: "External users are created, disabled or enabled only" (ACCESS_EXTERNAL_TYPE)
-MSG-UA-069: "Enter the full name of the new user" (ACCESS_FULL_NAME)
-MSG-UA-070: "Enter the justification" (ACCESS_JUSTIFICATION)
-MSG-UA-071: "The request does not change the user" (ACCESS_NOTHING_CHANGED)
-MSG-UA-072: "Only the creator can &lt;what&gt; request &lt;request no&gt;" (ACCESS_NOT_REQUESTER)
-MSG-UA-073: "A user request is decided by one approver" (ACCESS_ONE_APPROVER)
-MSG-UA-074: "A request for &lt;subject&gt; is already waiting for approval" (ACCESS_REQUEST_PENDING)
-MSG-UA-075: "Select the role to change" (ACCESS_ROLE)
-MSG-UA-076: "Select at least one role" (ACCESS_ROLES)
-MSG-UA-077: "Group profile &lt;name&gt; is not active" (ACCESS_ROLE_INACTIVE)
-MSG-UA-078: "One user may not hold both &lt;profile&gt; and &lt;other profile&gt; (separation-of-duties rule &lt;rule code&gt;)" (ACCESS_SOD_CONFLICT)
-MSG-UA-079: "Choose the type of request" (ACCESS_TYPE)
-MSG-UA-080: "Unknown role(s): &lt;unknown&gt;" (ACCESS_UNKNOWN_ROLE)
-MSG-UA-081: "User &lt;username&gt; does not exist" (ACCESS_UNKNOWN_USER)
-MSG-UA-082: "The user name has 3 to 50 letters, digits, dots, dashes or underscores" (ACCESS_USERNAME)
-MSG-UA-083: "User &lt;username&gt; is already active" (ACCESS_USER_ALREADY_ACTIVE)
-MSG-UA-084: "User &lt;username&gt; is already deactivated" (ACCESS_USER_ALREADY_INACTIVE)
-MSG-UA-085: "User &lt;username&gt; already exists" (ACCESS_USER_EXISTS)
-MSG-UA-086: "The user ID must be &lt;user id format text&gt;" (ACCESS_USER_ID_FORMAT)
-MSG-UA-087: "Windows ID &lt;windows id&gt; belongs to another user" (ACCESS_WINDOWS_ID_IN_USE)
-MSG-UA-088: "Access request not found: &lt;id&gt;" (NOT_FOUND)
-MSG-UA-089: "Access request not found: &lt;request no&gt;" (NOT_FOUND)
-MSG-UA-090: "You cannot change your own roles" (SELF_ROLE_CHANGE)</t>
+MSG-UA-036: "Add at least one approver"
+MSG-UA-037: "Enter an amount of zero or more, with up to 2 decimals"
+MSG-UA-038: "Enter the full name of the new user"
+MSG-UA-039: "Enter the justification"
+MSG-UA-040: "Enter the name of the group profile"
+MSG-UA-041: "Enter the party code"
+MSG-UA-042: "Enter the profile code"
+MSG-UA-043: "Grant or withdraw at least one permission"
+MSG-UA-044: "Select an existing user"
+MSG-UA-045: "Select at least one permission"
+MSG-UA-046: "Select at least one role"
+MSG-UA-047: "Select the approver"
+MSG-UA-048: "Select the insurer or client"
+MSG-UA-049: "Select the role to change"
+MSG-UA-050: "The effective date cannot be before today"
+MSG-UA-051: "The user ID does not have the required format"
+MSG-UA-052: "The user ID must be &lt;user id format text&gt;"
+MSG-UA-053: "This user already exists"
+MSG-UA-054: "This user is already active"
+MSG-UA-055: "This user is already deactivated"
+MSG-UA-056: "Use 3 to 50 letters, digits, dots, dashes or underscores"
+MSG-UA-057: "Use up to 40 capital letters, digits or underscores"
+MSG-UA-058: "&lt;name&gt; cannot approve this request" (ACCESS_APPROVER_NOT_ELIGIBLE)
+MSG-UA-059: "Add at least one approver" (ACCESS_APPROVER_REQUIRED)
+MSG-UA-060: "Select the approver" (ACCESS_APPROVER_REQUIRED)
+MSG-UA-061: "&lt;name&gt; is already an approver of this request" (ACCESS_APPROVER_TWICE)
+MSG-UA-062: "Enter the correction remarks" (ACCESS_CORRECTION_REMARKS)
+MSG-UA-063: "The effective date cannot be before today" (ACCESS_EFFECTIVE_DATE)
+MSG-UA-064: "An effective date applies to user requests; group profiles are implemented" (ACCESS_EFFECTIVE_DATE_USER_ONLY)
+MSG-UA-065: "Select the insurer or client of the external user" (ACCESS_EXTERNAL_PARTY)
+MSG-UA-066: "External users are created, disabled or enabled only" (ACCESS_EXTERNAL_TYPE)
+MSG-UA-067: "Enter the full name of the new user" (ACCESS_FULL_NAME)
+MSG-UA-068: "Enter the justification" (ACCESS_JUSTIFICATION)
+MSG-UA-069: "The request does not change the user" (ACCESS_NOTHING_CHANGED)
+MSG-UA-070: "Only the creator can &lt;what&gt; request &lt;request no&gt;" (ACCESS_NOT_REQUESTER)
+MSG-UA-071: "A user request is decided by one approver" (ACCESS_ONE_APPROVER)
+MSG-UA-072: "A request for &lt;subject&gt; is already waiting for approval" (ACCESS_REQUEST_PENDING)
+MSG-UA-073: "Select the role to change" (ACCESS_ROLE)
+MSG-UA-074: "Select at least one role" (ACCESS_ROLES)
+MSG-UA-075: "Group profile &lt;name&gt; is not active" (ACCESS_ROLE_INACTIVE)
+MSG-UA-076: "One user may not hold both &lt;profile&gt; and &lt;other profile&gt; (separation-of-duties rule &lt;rule code&gt;)" (ACCESS_SOD_CONFLICT)
+MSG-UA-077: "Choose the type of request" (ACCESS_TYPE)
+MSG-UA-078: "Unknown role(s): &lt;unknown&gt;" (ACCESS_UNKNOWN_ROLE)
+MSG-UA-079: "User &lt;username&gt; does not exist" (ACCESS_UNKNOWN_USER)
+MSG-UA-080: "The user name has 3 to 50 letters, digits, dots, dashes or underscores" (ACCESS_USERNAME)
+MSG-UA-081: "User &lt;username&gt; is already active" (ACCESS_USER_ALREADY_ACTIVE)
+MSG-UA-082: "User &lt;username&gt; is already deactivated" (ACCESS_USER_ALREADY_INACTIVE)
+MSG-UA-083: "User &lt;username&gt; already exists" (ACCESS_USER_EXISTS)
+MSG-UA-084: "The user ID must be &lt;user id format text&gt;" (ACCESS_USER_ID_FORMAT)
+MSG-UA-085: "Windows ID &lt;windows id&gt; belongs to another user" (ACCESS_WINDOWS_ID_IN_USE)
+MSG-UA-086: "Access request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-UA-087: "Access request not found: &lt;request no&gt;" (NOT_FOUND)
+MSG-UA-088: "You cannot change your own roles" (SELF_ROLE_CHANGE)</t>
         </is>
       </c>
       <c r="M204" s="12" t="inlineStr">
@@ -25497,26 +25495,26 @@
       <c r="L205" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-091: "Enter the &lt;label&gt;"
-MSG-UA-092: "The approvers are chosen on submission."
-MSG-UA-093: "Enter the reason for the cancellation" (ACCESS_CANCEL_REASON)
-MSG-UA-094: "A request cannot be decided by the user who submitted it" (ACCESS_FOUR_EYES)
-MSG-UA-095: "Enter the justification" (ACCESS_JUSTIFICATION)
-MSG-UA-096: "Request &lt;request no&gt; is assigned to &lt;assigned&gt; for approval" (ACCESS_NOT_ASSIGNED)
-MSG-UA-097: "Only &lt;created by&gt; can resubmit this request" (ACCESS_NOT_REQUESTER)
-MSG-UA-098: "Only the creator can cancel request &lt;request no&gt;" (ACCESS_NOT_REQUESTER)
-MSG-UA-099: "Request &lt;request no&gt; is &lt;status&gt;, not waiting for a second approval" (ACCESS_NOT_SECOND_APPROVAL)
-MSG-UA-100: "Enter the reason of the rejection" (ACCESS_REJECT_REASON)
-MSG-UA-101: "Request &lt;request no&gt; is already &lt;status&gt;" (ACCESS_REQUEST_DECIDED)
-MSG-UA-102: "Request &lt;request no&gt; is &lt;status&gt;, not returned" (ACCESS_REQUEST_NOT_RETURNED)
-MSG-UA-103: "The type of request &lt;request no&gt; cannot change" (ACCESS_REQUEST_TYPE_FIXED)
-MSG-UA-104: "Enter the remarks for the requester" (ACCESS_RETURN_REASON)
-MSG-UA-105: "Request &lt;request no&gt; waits for the second approval" (ACCESS_SECOND_APPROVAL_PENDING)
-MSG-UA-106: "The second approval is given by another approver" (ACCESS_SECOND_SAME_APPROVER)
-MSG-UA-107: "You cannot decide a request about your own access" (ACCESS_SUBJECT_DECIDES)
-MSG-UA-108: "External (portal) users are not available: the portal is not installed" (NOT_AVAILABLE)
-MSG-UA-109: "Access request not found: &lt;id&gt;" (NOT_FOUND)
-MSG-UA-110: "Role not found: &lt;code&gt;" (NOT_FOUND)</t>
+MSG-UA-089: "Enter the &lt;label&gt;"
+MSG-UA-090: "The approvers are chosen on submission."
+MSG-UA-091: "Enter the reason for the cancellation" (ACCESS_CANCEL_REASON)
+MSG-UA-092: "A request cannot be decided by the user who submitted it" (ACCESS_FOUR_EYES)
+MSG-UA-093: "Enter the justification" (ACCESS_JUSTIFICATION)
+MSG-UA-094: "Request &lt;request no&gt; is assigned to &lt;assigned&gt; for approval" (ACCESS_NOT_ASSIGNED)
+MSG-UA-095: "Only &lt;created by&gt; can resubmit this request" (ACCESS_NOT_REQUESTER)
+MSG-UA-096: "Only the creator can cancel request &lt;request no&gt;" (ACCESS_NOT_REQUESTER)
+MSG-UA-097: "Request &lt;request no&gt; is &lt;status&gt;, not waiting for a second approval" (ACCESS_NOT_SECOND_APPROVAL)
+MSG-UA-098: "Enter the reason of the rejection" (ACCESS_REJECT_REASON)
+MSG-UA-099: "Request &lt;request no&gt; is already &lt;status&gt;" (ACCESS_REQUEST_DECIDED)
+MSG-UA-100: "Request &lt;request no&gt; is &lt;status&gt;, not returned" (ACCESS_REQUEST_NOT_RETURNED)
+MSG-UA-101: "The type of request &lt;request no&gt; cannot change" (ACCESS_REQUEST_TYPE_FIXED)
+MSG-UA-102: "Enter the remarks for the requester" (ACCESS_RETURN_REASON)
+MSG-UA-103: "Request &lt;request no&gt; waits for the second approval" (ACCESS_SECOND_APPROVAL_PENDING)
+MSG-UA-104: "The second approval is given by another approver" (ACCESS_SECOND_SAME_APPROVER)
+MSG-UA-105: "You cannot decide a request about your own access" (ACCESS_SUBJECT_DECIDES)
+MSG-UA-106: "External (portal) users are not available: the portal is not installed" (NOT_AVAILABLE)
+MSG-UA-107: "Access request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-UA-108: "Role not found: &lt;code&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M205" s="12" t="inlineStr">
@@ -25591,8 +25589,8 @@
       <c r="L206" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-113: "Action &lt;action&gt; is not valid" (ACCESS_BULK_ACTION)
-MSG-UA-114: "Unknown branch &lt;code&gt;" (ACCESS_BULK_BRANCH)</t>
+MSG-UA-111: "Action &lt;action&gt; is not valid" (ACCESS_BULK_ACTION)
+MSG-UA-112: "Unknown branch &lt;code&gt;" (ACCESS_BULK_BRANCH)</t>
         </is>
       </c>
       <c r="M206" s="12" t="inlineStr">
@@ -25667,11 +25665,11 @@
       <c r="L207" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-115: "Batch &lt;batch no&gt; has no draft" (ACCESS_BATCH_NOTHING_TO_SUBMIT)
-MSG-UA-116: "Batch &lt;batch no&gt; has no line to decide" (ACCESS_BATCH_NO_LINE)
-MSG-UA-117: "Enter the justification" (ACCESS_JUSTIFICATION)
-MSG-UA-118: "Only the creator can submit batch &lt;batch no&gt;" (ACCESS_NOT_REQUESTER)
-MSG-UA-119: "Batch not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-UA-113: "Batch &lt;batch no&gt; has no draft" (ACCESS_BATCH_NOTHING_TO_SUBMIT)
+MSG-UA-114: "Batch &lt;batch no&gt; has no line to decide" (ACCESS_BATCH_NO_LINE)
+MSG-UA-115: "Enter the justification" (ACCESS_JUSTIFICATION)
+MSG-UA-116: "Only the creator can submit batch &lt;batch no&gt;" (ACCESS_NOT_REQUESTER)
+MSG-UA-117: "Batch not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M207" s="12" t="inlineStr">
@@ -25746,19 +25744,19 @@
       <c r="L208" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-120: "Select at least one permission" (ACCESS_NO_PERMISSION)
-MSG-UA-121: "The request does not change the permissions of group profile &lt;name&gt;" (ACCESS_NO_PERMISSION_CHANGE)
-MSG-UA-122: "Permission(s) both added and removed: &lt;overlap&gt;" (ACCESS_PERMISSION_CONFLICT)
-MSG-UA-123: "Split the change into several requests" (ACCESS_PERMISSION_LIST_TOO_LONG)
-MSG-UA-124: "Select the role to change" (ACCESS_ROLE)
-MSG-UA-125: "Group profile &lt;name&gt; is already active" (ACCESS_ROLE_ALREADY_ACTIVE)
-MSG-UA-126: "Group profile &lt;name&gt; is already inactive" (ACCESS_ROLE_ALREADY_INACTIVE)
-MSG-UA-127: "The profile code has up to 40 capital letters, digits or underscores" (ACCESS_ROLE_CODE)
-MSG-UA-128: "Enter the name of the group profile" (ACCESS_ROLE_NAME)
-MSG-UA-129: "Group profile &lt;name&gt; cannot be deactivated" (ACCESS_ROLE_PROTECTED)
-MSG-UA-130: "Unknown permission(s): &lt;unknown&gt;" (ACCESS_UNKNOWN_PERMISSION)
-MSG-UA-131: "Unknown role(s): &lt;code&gt;" (ACCESS_UNKNOWN_ROLE)
-MSG-UA-132: "Role &lt;code&gt; already exists" (DUPLICATE)</t>
+MSG-UA-118: "Select at least one permission" (ACCESS_NO_PERMISSION)
+MSG-UA-119: "The request does not change the permissions of group profile &lt;name&gt;" (ACCESS_NO_PERMISSION_CHANGE)
+MSG-UA-120: "Permission(s) both added and removed: &lt;overlap&gt;" (ACCESS_PERMISSION_CONFLICT)
+MSG-UA-121: "Split the change into several requests" (ACCESS_PERMISSION_LIST_TOO_LONG)
+MSG-UA-122: "Select the role to change" (ACCESS_ROLE)
+MSG-UA-123: "Group profile &lt;name&gt; is already active" (ACCESS_ROLE_ALREADY_ACTIVE)
+MSG-UA-124: "Group profile &lt;name&gt; is already inactive" (ACCESS_ROLE_ALREADY_INACTIVE)
+MSG-UA-125: "The profile code has up to 40 capital letters, digits or underscores" (ACCESS_ROLE_CODE)
+MSG-UA-126: "Enter the name of the group profile" (ACCESS_ROLE_NAME)
+MSG-UA-127: "Group profile &lt;name&gt; cannot be deactivated" (ACCESS_ROLE_PROTECTED)
+MSG-UA-128: "Unknown permission(s): &lt;unknown&gt;" (ACCESS_UNKNOWN_PERMISSION)
+MSG-UA-129: "Unknown role(s): &lt;code&gt;" (ACCESS_UNKNOWN_ROLE)
+MSG-UA-130: "Role &lt;code&gt; already exists" (DUPLICATE)</t>
         </is>
       </c>
       <c r="M208" s="12" t="inlineStr">
@@ -25833,8 +25831,8 @@
       <c r="L209" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-134: "The as-of date cannot be in the future" (AS_OF_IN_FUTURE)
-MSG-UA-135: "The end date must be on or after the start date" (DATE_RANGE_REVERSED)</t>
+MSG-UA-132: "The as-of date cannot be in the future" (AS_OF_IN_FUTURE)
+MSG-UA-133: "The end date must be on or after the start date" (DATE_RANGE_REVERSED)</t>
         </is>
       </c>
       <c r="M209" s="12" t="inlineStr">
@@ -25909,16 +25907,16 @@
       <c r="L210" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-138: "Role already exists: &lt;key&gt;" (DUPLICATE)
-MSG-UA-139: "User already exists: &lt;key&gt;" (DUPLICATE)
-MSG-UA-140: "Current password is incorrect" (INVALID_PASSWORD)
-MSG-UA-141: "Role not found: &lt;id&gt;" (NOT_FOUND)
-MSG-UA-142: "User not found: &lt;id&gt;" (NOT_FOUND)
-MSG-UA-143: "User not found: &lt;username&gt;" (NOT_FOUND)
-MSG-UA-144: "Permission(s) not available in BIBS: &lt;insurer only&gt;" (PERMISSION_NOT_OFFERED)
-MSG-UA-145: "You cannot change your own roles" (SELF_ROLE_CHANGE)
-MSG-UA-146: "One or more roles do not exist: &lt;role codes&gt;" (UNKNOWN_ROLE)
-MSG-UA-147: "Windows ID &lt;windows id&gt; is already used by another user" (WINDOWS_ID_IN_USE)</t>
+MSG-UA-136: "Role already exists: &lt;key&gt;" (DUPLICATE)
+MSG-UA-137: "User already exists: &lt;key&gt;" (DUPLICATE)
+MSG-UA-138: "Current password is incorrect" (INVALID_PASSWORD)
+MSG-UA-139: "Role not found: &lt;id&gt;" (NOT_FOUND)
+MSG-UA-140: "User not found: &lt;id&gt;" (NOT_FOUND)
+MSG-UA-141: "User not found: &lt;username&gt;" (NOT_FOUND)
+MSG-UA-142: "Permission(s) not available in BIBS: &lt;insurer only&gt;" (PERMISSION_NOT_OFFERED)
+MSG-UA-143: "You cannot change your own roles" (SELF_ROLE_CHANGE)
+MSG-UA-144: "One or more roles do not exist: &lt;role codes&gt;" (UNKNOWN_ROLE)
+MSG-UA-145: "Windows ID &lt;windows id&gt; is already used by another user" (WINDOWS_ID_IN_USE)</t>
         </is>
       </c>
       <c r="M210" s="12" t="inlineStr">
@@ -25993,13 +25991,13 @@
       <c r="L211" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-151: "A request is implemented by someone other than its requester" (ACCESS_IMPLEMENTER_IS_REQUESTER)
-MSG-UA-152: "Request &lt;request no&gt; is &lt;status&gt;, not waiting for implementation" (ACCESS_REQUEST_NOT_FOR_IMPLEMENTATION)
-MSG-UA-153: "Access request not found: &lt;id&gt;" (NOT_FOUND)
-MSG-UA-154: "Role &lt;code&gt; is already active" (ROLE_ALREADY_ACTIVE)
-MSG-UA-155: "Role &lt;code&gt; is already inactive" (ROLE_ALREADY_INACTIVE)
-MSG-UA-156: "Roles are changed through an approved group-profile request; implement the request instead" (ROLE_EDIT_BY_REQUEST)
-MSG-UA-157: "Request &lt;request no&gt; is not an approved group-profile request for role &lt;role code&gt;" (ROLE_REQUEST_NOT_APPROVED)</t>
+MSG-UA-149: "A request is implemented by someone other than its requester" (ACCESS_IMPLEMENTER_IS_REQUESTER)
+MSG-UA-150: "Request &lt;request no&gt; is &lt;status&gt;, not waiting for implementation" (ACCESS_REQUEST_NOT_FOR_IMPLEMENTATION)
+MSG-UA-151: "Access request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-UA-152: "Role &lt;code&gt; is already active" (ROLE_ALREADY_ACTIVE)
+MSG-UA-153: "Role &lt;code&gt; is already inactive" (ROLE_ALREADY_INACTIVE)
+MSG-UA-154: "Roles are changed through an approved group-profile request; implement the request instead" (ROLE_EDIT_BY_REQUEST)
+MSG-UA-155: "Request &lt;request no&gt; is not an approved group-profile request for role &lt;role code&gt;" (ROLE_REQUEST_NOT_APPROVED)</t>
         </is>
       </c>
       <c r="M211" s="12" t="inlineStr">
@@ -26074,12 +26072,12 @@
       <c r="L212" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-158: "Enter the reason for the rejection"
-MSG-UA-159: "&lt;key&gt; is too long" (INVALID_PARAMETER_VALUE)
-MSG-UA-160: "A change cannot be approved by the user who requested it" (MAKER_CHECKER_VIOLATION)
-MSG-UA-161: "A change of &lt;key&gt; already waits for approval; approve or reject it first" (PARAMETER_CHANGE_PENDING)
-MSG-UA-162: "No change of &lt;key&gt; waits for approval" (PARAMETER_NO_PENDING_CHANGE)
-MSG-UA-163: "Give the reason for the rejection" (REASON_REQUIRED)</t>
+MSG-UA-156: "Enter the reason for the rejection"
+MSG-UA-157: "&lt;key&gt; is too long" (INVALID_PARAMETER_VALUE)
+MSG-UA-158: "A change cannot be approved by the user who requested it" (MAKER_CHECKER_VIOLATION)
+MSG-UA-159: "A change of &lt;key&gt; already waits for approval; approve or reject it first" (PARAMETER_CHANGE_PENDING)
+MSG-UA-160: "No change of &lt;key&gt; waits for approval" (PARAMETER_NO_PENDING_CHANGE)
+MSG-UA-161: "Give the reason for the rejection" (REASON_REQUIRED)</t>
         </is>
       </c>
       <c r="M212" s="12" t="inlineStr">
@@ -26154,21 +26152,21 @@
       <c r="L213" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-164: "Choose two different group profiles"
-MSG-UA-165: "Enter why the two profiles are not held together"
-MSG-UA-169: "Select the first group profile"
-MSG-UA-170: "Select the second group profile"
-MSG-UA-171: "The deactivation is sent to Information Security; the rule stays active until it is authorised."
-MSG-UA-172: "The pending change is rejected and the rule stays as it was."
-MSG-UA-173: "A record cannot be authorized by the user who maintained it" (MAKER_CHECKER_VIOLATION)
-MSG-UA-174: "Separation of duties rule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-UA-175: "Give the reason for the rejection" (REASON_REQUIRED)
-MSG-UA-176: "Enter why the two profiles are not held together" (SOD_DESCRIPTION)
-MSG-UA-177: "A rule for these two group profiles already exists" (SOD_RULE_EXISTS)
-MSG-UA-178: "Rule &lt;rule code&gt; does not wait for an authorisation" (SOD_RULE_NOT_PENDING)
-MSG-UA-179: "Rule &lt;rule code&gt; is not active or already waits for an authorisation" (SOD_RULE_NOT_PENDING)
-MSG-UA-180: "Choose two different group profiles" (SOD_SAME_PROFILE)
-MSG-UA-181: "Choose the group profiles from the list" (SOD_UNKNOWN_PROFILE)</t>
+MSG-UA-162: "Choose two different group profiles"
+MSG-UA-163: "Enter why the two profiles are not held together"
+MSG-UA-167: "Select the first group profile"
+MSG-UA-168: "Select the second group profile"
+MSG-UA-169: "The deactivation is sent to Information Security; the rule stays active until it is authorised."
+MSG-UA-170: "The pending change is rejected and the rule stays as it was."
+MSG-UA-171: "A record cannot be authorized by the user who maintained it" (MAKER_CHECKER_VIOLATION)
+MSG-UA-172: "Separation of duties rule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-UA-173: "Give the reason for the rejection" (REASON_REQUIRED)
+MSG-UA-174: "Enter why the two profiles are not held together" (SOD_DESCRIPTION)
+MSG-UA-175: "A rule for these two group profiles already exists" (SOD_RULE_EXISTS)
+MSG-UA-176: "Rule &lt;rule code&gt; does not wait for an authorisation" (SOD_RULE_NOT_PENDING)
+MSG-UA-177: "Rule &lt;rule code&gt; is not active or already waits for an authorisation" (SOD_RULE_NOT_PENDING)
+MSG-UA-178: "Choose two different group profiles" (SOD_SAME_PROFILE)
+MSG-UA-179: "Choose the group profiles from the list" (SOD_UNKNOWN_PROFILE)</t>
         </is>
       </c>
       <c r="M213" s="12" t="inlineStr">
@@ -26193,19 +26191,11 @@
         </is>
       </c>
       <c r="B214" s="12" t="inlineStr"/>
-      <c r="C214" s="12" t="inlineStr">
-        <is>
-          <t>FR-UA-019</t>
-        </is>
-      </c>
-      <c r="D214" s="12" t="inlineStr">
-        <is>
-          <t>BRD 1.009.1, BRD 1.009.1.1, BRD 1.009.1.2, BRD 1.009.1.3, BRD 1.009.1.4, BRD 1.009.1.5, BRD 1.009.1.6, UAM-NFR-38</t>
-        </is>
-      </c>
+      <c r="C214" s="12" t="inlineStr"/>
+      <c r="D214" s="12" t="inlineStr"/>
       <c r="E214" s="12" t="inlineStr">
         <is>
-          <t>Messages of Bulk Request (SCR-UA-09): every upload type</t>
+          <t>Messages of Several screens</t>
         </is>
       </c>
       <c r="F214" s="12" t="inlineStr">
@@ -26220,14 +26210,10 @@
       </c>
       <c r="H214" s="12" t="inlineStr">
         <is>
-          <t>Setup &amp; Administration › User Access › Bulk Request</t>
-        </is>
-      </c>
-      <c r="I214" s="12" t="inlineStr">
-        <is>
-          <t>SCR-UA-09</t>
-        </is>
-      </c>
+          <t>Any User Access Maintenance record</t>
+        </is>
+      </c>
+      <c r="I214" s="12" t="inlineStr"/>
       <c r="J214" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
@@ -26236,15 +26222,37 @@
       <c r="K214" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as requestor.
-2. Open Setup &amp; Administration › User Access › Bulk Request.
+2. Open Any User Access Maintenance record.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
       <c r="L214" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-182: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
-MSG-UA-183: "&lt;Column&gt; is mandatory"</t>
+MSG-UA-180: "The sign-in could not be completed. Start again from the sign-in page."
+MSG-UA-181: "Your organisation’s sign-in service could not complete the sign-in. Try again in a moment."
+MSG-UA-182: "Your sign-in was accepted by your organisation, but it is not linked to an active user of this system. Contact your administrator."
+MSG-UA-185: "Only an approver or the requester may close this request" (ACCESS_DENIED)
+MSG-UA-187: "Invalid user name or password" (AUTHENTICATION_FAILED)
+MSG-UA-188: "The sign-in link is not valid" (AUTHENTICATION_FAILED)
+MSG-UA-189: "Your session has ended. Sign in again." (AUTHENTICATION_FAILED)
+MSG-UA-191: "Another administrator must approve a reset you requested" (FOUR_EYES)
+MSG-UA-192: "You cannot approve the reset of your own second factor" (FOUR_EYES)
+MSG-UA-196: "The code does not match" (MFA_CODE_INVALID)
+MSG-UA-197: "The code does not match. Check the time of your phone and retry" (MFA_CODE_INVALID)
+MSG-UA-198: "Start the enrolment of the app first" (MFA_ENROLMENT_NOT_STARTED)
+MSG-UA-199: "The second factor is not set up on this system" (MFA_NOT_AVAILABLE)
+MSG-UA-200: "No authenticator app" (MFA_NOT_ENROLLED)
+MSG-UA-201: "This user has no authenticator app to reset" (MFA_NOT_ENROLLED)
+MSG-UA-202: "A reset of this user's second factor already waits for approval" (MFA_RESET_PENDING)
+MSG-UA-203: "Second factor reset request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-UA-204: "System parameter not found: &lt;key&gt;" (NOT_FOUND)
+MSG-UA-205: "User not found: &lt;username&gt;" (NOT_FOUND)
+MSG-UA-206: "Business parameter &lt;key&gt; has no value" (PARAMETER_NOT_SET)
+MSG-UA-207: "Give the reason for the rejection" (REASON_REQUIRED)
+MSG-UA-208: "Give the reason for the reset" (REASON_REQUIRED)
+MSG-UA-209: "This request is already closed" (REQUEST_CLOSED)
+MSG-UA-210: "The sign-in could not be checked. Try again in a moment." (SIGN_IN_CHECK_UNAVAILABLE)</t>
         </is>
       </c>
       <c r="M214" s="12" t="inlineStr">
@@ -26269,11 +26277,19 @@
         </is>
       </c>
       <c r="B215" s="12" t="inlineStr"/>
-      <c r="C215" s="12" t="inlineStr"/>
-      <c r="D215" s="12" t="inlineStr"/>
+      <c r="C215" s="12" t="inlineStr">
+        <is>
+          <t>FR-UA-019</t>
+        </is>
+      </c>
+      <c r="D215" s="12" t="inlineStr">
+        <is>
+          <t>BRD 1.009.1, BRD 1.009.1.1, BRD 1.009.1.2, BRD 1.009.1.3, BRD 1.009.1.4, BRD 1.009.1.5, BRD 1.009.1.6, UAM-NFR-38</t>
+        </is>
+      </c>
       <c r="E215" s="12" t="inlineStr">
         <is>
-          <t>Messages of Every screen (Common screen elements)</t>
+          <t>Messages of Bulk Request (SCR-UA-09): every upload type</t>
         </is>
       </c>
       <c r="F215" s="12" t="inlineStr">
@@ -26288,10 +26304,14 @@
       </c>
       <c r="H215" s="12" t="inlineStr">
         <is>
-          <t>Any User Access Maintenance record</t>
-        </is>
-      </c>
-      <c r="I215" s="12" t="inlineStr"/>
+          <t>Setup &amp; Administration › User Access › Bulk Request</t>
+        </is>
+      </c>
+      <c r="I215" s="12" t="inlineStr">
+        <is>
+          <t>SCR-UA-09</t>
+        </is>
+      </c>
       <c r="J215" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
@@ -26300,20 +26320,15 @@
       <c r="K215" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as requestor.
-2. Open Any User Access Maintenance record.
+2. Open Setup &amp; Administration › User Access › Bulk Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
       <c r="L215" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-184: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-UA-185: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-UA-186: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
-MSG-UA-187: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-UA-188: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-UA-190: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-UA-191: "Invalid request" (VALIDATION_FAILED)</t>
+MSG-UA-183: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
+MSG-UA-184: "&lt;Column&gt; is mandatory"</t>
         </is>
       </c>
       <c r="M215" s="12" t="inlineStr">
@@ -26342,7 +26357,7 @@
       <c r="D216" s="12" t="inlineStr"/>
       <c r="E216" s="12" t="inlineStr">
         <is>
-          <t>Messages of Several screens</t>
+          <t>Messages of Every screen (Common screen elements)</t>
         </is>
       </c>
       <c r="F216" s="12" t="inlineStr">
@@ -26376,7 +26391,13 @@
       <c r="L216" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-UA-189: "System parameter not found: &lt;key&gt;" (NOT_FOUND)</t>
+MSG-UA-186: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-UA-190: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-UA-193: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
+MSG-UA-194: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-UA-195: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-UA-211: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-UA-212: "Invalid request" (VALIDATION_FAILED)</t>
         </is>
       </c>
       <c r="M216" s="12" t="inlineStr">
@@ -33944,7 +33965,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>TC-UA-019.1-01, TC-UA-019.2-01, TC-UA-019.2-02, TC-UA-019.3-01, TC-UA-019.4-01, TC-UA-053.3-01, TC-UA-SCR-09, TC-UA-MSG-09, TC-UA-MSG-17</t>
+          <t>TC-UA-019.1-01, TC-UA-019.2-01, TC-UA-019.2-02, TC-UA-019.3-01, TC-UA-019.4-01, TC-UA-053.3-01, TC-UA-SCR-09, TC-UA-MSG-09, TC-UA-MSG-18</t>
         </is>
       </c>
     </row>
